--- a/Output/ModelAggregates/ExploratoryModels.xlsx
+++ b/Output/ModelAggregates/ExploratoryModels.xlsx
@@ -6085,7 +6085,7 @@
         </is>
       </c>
       <c r="D130">
-        <v>42.02</v>
+        <v>57.98</v>
       </c>
       <c r="E130">
         <v>3.185</v>
@@ -6094,10 +6094,10 @@
         <v>51.969</v>
       </c>
       <c r="G130">
-        <v>35.629</v>
+        <v>51.589</v>
       </c>
       <c r="H130">
-        <v>48.411</v>
+        <v>64.371</v>
       </c>
       <c r="I130">
         <v>0</v>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="D131">
-        <v>0.131</v>
+        <v>-0.131</v>
       </c>
       <c r="E131">
         <v>4.316</v>
@@ -6137,10 +6137,10 @@
         <v>47.33</v>
       </c>
       <c r="G131">
-        <v>-8.551</v>
+        <v>-8.813000000000001</v>
       </c>
       <c r="H131">
-        <v>8.813000000000001</v>
+        <v>8.551</v>
       </c>
       <c r="I131">
         <v>0.976</v>
@@ -6171,7 +6171,7 @@
         </is>
       </c>
       <c r="D132">
-        <v>17.563</v>
+        <v>-17.563</v>
       </c>
       <c r="E132">
         <v>8.461</v>
@@ -6180,10 +6180,10 @@
         <v>50.135</v>
       </c>
       <c r="G132">
-        <v>0.5679999999999999</v>
+        <v>-34.557</v>
       </c>
       <c r="H132">
-        <v>34.557</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="I132">
         <v>0.043</v>
@@ -6214,7 +6214,7 @@
         </is>
       </c>
       <c r="D133">
-        <v>9.362</v>
+        <v>-9.362</v>
       </c>
       <c r="E133">
         <v>6.043</v>
@@ -6223,10 +6223,10 @@
         <v>45.048</v>
       </c>
       <c r="G133">
-        <v>-2.809</v>
+        <v>-21.532</v>
       </c>
       <c r="H133">
-        <v>21.532</v>
+        <v>2.809</v>
       </c>
       <c r="I133">
         <v>0.128</v>
@@ -6263,7 +6263,7 @@
         </is>
       </c>
       <c r="D134">
-        <v>44.597</v>
+        <v>55.403</v>
       </c>
       <c r="E134">
         <v>5.025</v>
@@ -6272,10 +6272,10 @@
         <v>49.863</v>
       </c>
       <c r="G134">
-        <v>34.502</v>
+        <v>45.309</v>
       </c>
       <c r="H134">
-        <v>54.691</v>
+        <v>65.498</v>
       </c>
       <c r="I134">
         <v>0</v>
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="D135">
-        <v>7.269</v>
+        <v>-7.269</v>
       </c>
       <c r="E135">
         <v>7.491</v>
@@ -6315,10 +6315,10 @@
         <v>43.136</v>
       </c>
       <c r="G135">
-        <v>-7.836</v>
+        <v>-22.374</v>
       </c>
       <c r="H135">
-        <v>22.374</v>
+        <v>7.836</v>
       </c>
       <c r="I135">
         <v>0.337</v>
@@ -6349,7 +6349,7 @@
         </is>
       </c>
       <c r="D136">
-        <v>17.413</v>
+        <v>-17.413</v>
       </c>
       <c r="E136">
         <v>8.441000000000001</v>
@@ -6358,10 +6358,10 @@
         <v>47.278</v>
       </c>
       <c r="G136">
-        <v>0.435</v>
+        <v>-34.39</v>
       </c>
       <c r="H136">
-        <v>34.39</v>
+        <v>-0.435</v>
       </c>
       <c r="I136">
         <v>0.045</v>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="D137">
-        <v>-1.001</v>
+        <v>1.001</v>
       </c>
       <c r="E137">
         <v>1.504</v>
@@ -6401,10 +6401,10 @@
         <v>49.235</v>
       </c>
       <c r="G137">
-        <v>-4.023</v>
+        <v>-2.02</v>
       </c>
       <c r="H137">
-        <v>2.02</v>
+        <v>4.023</v>
       </c>
       <c r="I137">
         <v>0.509</v>
@@ -6435,7 +6435,7 @@
         </is>
       </c>
       <c r="D138">
-        <v>6.492</v>
+        <v>-6.492</v>
       </c>
       <c r="E138">
         <v>9.536</v>
@@ -6444,10 +6444,10 @@
         <v>41.684</v>
       </c>
       <c r="G138">
-        <v>-12.757</v>
+        <v>-25.74</v>
       </c>
       <c r="H138">
-        <v>25.74</v>
+        <v>12.757</v>
       </c>
       <c r="I138">
         <v>0.5</v>
@@ -6478,7 +6478,7 @@
         </is>
       </c>
       <c r="D139">
-        <v>-2.26</v>
+        <v>2.26</v>
       </c>
       <c r="E139">
         <v>2.129</v>
@@ -6487,10 +6487,10 @@
         <v>44.636</v>
       </c>
       <c r="G139">
-        <v>-6.548</v>
+        <v>-2.029</v>
       </c>
       <c r="H139">
-        <v>2.029</v>
+        <v>6.548</v>
       </c>
       <c r="I139">
         <v>0.294</v>
@@ -6521,7 +6521,7 @@
         </is>
       </c>
       <c r="D140">
-        <v>-0.13</v>
+        <v>0.13</v>
       </c>
       <c r="E140">
         <v>2.939</v>
@@ -6530,10 +6530,10 @@
         <v>43.734</v>
       </c>
       <c r="G140">
-        <v>-6.055</v>
+        <v>-5.795</v>
       </c>
       <c r="H140">
-        <v>5.795</v>
+        <v>6.055</v>
       </c>
       <c r="I140">
         <v>0.965</v>
@@ -11165,10 +11165,10 @@
         <v>49.518</v>
       </c>
       <c r="G245">
-        <v>1789.761</v>
+        <v>1825.571</v>
       </c>
       <c r="H245">
-        <v>2336.936</v>
+        <v>2301.126</v>
       </c>
       <c r="I245">
         <v>0</v>
@@ -11208,10 +11208,10 @@
         <v>45.71</v>
       </c>
       <c r="G246">
-        <v>-220.281</v>
+        <v>-206.067</v>
       </c>
       <c r="H246">
-        <v>-3.839</v>
+        <v>-18.053</v>
       </c>
       <c r="I246">
         <v>0.021</v>
@@ -11251,10 +11251,10 @@
         <v>47.285</v>
       </c>
       <c r="G247">
-        <v>-264.423</v>
+        <v>-240.303</v>
       </c>
       <c r="H247">
-        <v>103.403</v>
+        <v>79.28400000000001</v>
       </c>
       <c r="I247">
         <v>0.316</v>
@@ -11294,10 +11294,10 @@
         <v>49.76</v>
       </c>
       <c r="G248">
-        <v>181.523</v>
+        <v>234.162</v>
       </c>
       <c r="H248">
-        <v>986.021</v>
+        <v>933.381</v>
       </c>
       <c r="I248">
         <v>0.002</v>
@@ -11337,10 +11337,10 @@
         <v>48.319</v>
       </c>
       <c r="G249">
-        <v>-139.336</v>
+        <v>-128.498</v>
       </c>
       <c r="H249">
-        <v>26.094</v>
+        <v>15.257</v>
       </c>
       <c r="I249">
         <v>0.12</v>
@@ -11380,10 +11380,10 @@
         <v>42.074</v>
       </c>
       <c r="G250">
-        <v>10.475</v>
+        <v>40.439</v>
       </c>
       <c r="H250">
-        <v>464.968</v>
+        <v>435.005</v>
       </c>
       <c r="I250">
         <v>0.019</v>
@@ -11423,10 +11423,10 @@
         <v>45.823</v>
       </c>
       <c r="G251">
-        <v>-31.039</v>
+        <v>-26.599</v>
       </c>
       <c r="H251">
-        <v>36.587</v>
+        <v>32.147</v>
       </c>
       <c r="I251">
         <v>0.85</v>
@@ -11466,10 +11466,10 @@
         <v>47.974</v>
       </c>
       <c r="G252">
-        <v>-47.249</v>
+        <v>-40.231</v>
       </c>
       <c r="H252">
-        <v>59.847</v>
+        <v>52.829</v>
       </c>
       <c r="I252">
         <v>0.787</v>
@@ -11509,10 +11509,10 @@
         <v>40.873</v>
       </c>
       <c r="G253">
-        <v>-116.191</v>
+        <v>-106.325</v>
       </c>
       <c r="H253">
-        <v>33.25</v>
+        <v>23.384</v>
       </c>
       <c r="I253">
         <v>0.204</v>
